--- a/sheets/조재수대금교본/검수/섬집 아기.xlsx
+++ b/sheets/조재수대금교본/검수/섬집 아기.xlsx
@@ -5491,8 +5491,7 @@
       <c r="T3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㑣
-黃
-c</t>
+黃</t>
         </is>
       </c>
       <c r="U3" s="22"/>
@@ -5639,8 +5638,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C6" s="27"/>
@@ -5650,30 +5648,23 @@
         </is>
       </c>
       <c r="E6" s="27"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="27"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I6" s="27"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㑣
-‹</t>
+          <t xml:space="preserve">㑣</t>
         </is>
       </c>
       <c r="K6" s="27"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M6" s="27"/>
@@ -5683,23 +5674,11 @@
         </is>
       </c>
       <c r="O6" s="27"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P6" s="21"/>
       <c r="Q6" s="27"/>
-      <c r="R6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R6" s="21"/>
       <c r="S6" s="27"/>
-      <c r="T6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T6" s="21"/>
       <c r="U6" s="27"/>
     </row>
     <row r="7" ht="117.77" customHeight="true">
@@ -5862,8 +5841,7 @@
       <c r="G9" s="25"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I9" s="25"/>
@@ -5902,19 +5880,11 @@
     </row>
     <row r="10" ht="117.77" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="27"/>
       <c r="D10" s="21"/>
       <c r="E10" s="27"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="27"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
@@ -5924,37 +5894,17 @@
         </is>
       </c>
       <c r="I10" s="27"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="27"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="27"/>
       <c r="N10" s="21"/>
       <c r="O10" s="27"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="27"/>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R10" s="21"/>
       <c r="S10" s="27"/>
-      <c r="T10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T10" s="21"/>
       <c r="U10" s="27"/>
     </row>
     <row r="11" ht="117.77" customHeight="true">
@@ -6078,11 +6028,7 @@
         </is>
       </c>
       <c r="O12" s="25"/>
-      <c r="P12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P12" s="21"/>
       <c r="Q12" s="25"/>
       <c r="R12" s="21" t="inlineStr">
         <is>
@@ -6172,8 +6118,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㑣
-‹</t>
+          <t xml:space="preserve">㑣</t>
         </is>
       </c>
       <c r="C14" s="27"/>
@@ -6183,25 +6128,19 @@
         </is>
       </c>
       <c r="E14" s="27"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="27"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="I14" s="27"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㑣
-‹</t>
+          <t xml:space="preserve">㑣</t>
         </is>
       </c>
       <c r="K14" s="27"/>
@@ -6209,8 +6148,7 @@
         <is>
           <t xml:space="preserve">㴌
 –
-㴌
-‹</t>
+㴌</t>
         </is>
       </c>
       <c r="M14" s="27"/>
@@ -6220,23 +6158,11 @@
         </is>
       </c>
       <c r="O14" s="27"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="27"/>
-      <c r="R14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R14" s="21"/>
       <c r="S14" s="27"/>
-      <c r="T14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T14" s="21"/>
       <c r="U14" s="27"/>
     </row>
     <row r="15" ht="117.77" customHeight="true">
@@ -6350,8 +6276,7 @@
         <is>
           <t xml:space="preserve">林
 –
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="M16" s="25"/>
@@ -6449,11 +6374,7 @@
       <c r="C18" s="27"/>
       <c r="D18" s="21"/>
       <c r="E18" s="27"/>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F18" s="21"/>
       <c r="G18" s="27"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
@@ -6463,11 +6384,7 @@
         </is>
       </c>
       <c r="I18" s="27"/>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J18" s="21"/>
       <c r="K18" s="27"/>
       <c r="L18" s="21" t="inlineStr">
         <is>
@@ -6479,11 +6396,7 @@
       <c r="M18" s="27"/>
       <c r="N18" s="21"/>
       <c r="O18" s="27"/>
-      <c r="P18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P18" s="21"/>
       <c r="Q18" s="27"/>
       <c r="R18" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/섬집 아기.xlsx
+++ b/sheets/조재수대금교본/검수/섬집 아기.xlsx
@@ -5491,7 +5491,8 @@
       <c r="T3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㑣
-黃</t>
+黃
+c</t>
         </is>
       </c>
       <c r="U3" s="22"/>

--- a/sheets/조재수대금교본/검수/섬집 아기.xlsx
+++ b/sheets/조재수대금교본/검수/섬집 아기.xlsx
@@ -5376,32 +5376,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="105.26" customHeight="true">
+    <row r="2" ht="86.96" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="117.77" customHeight="true">
+    <row r="3" ht="97.23" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="117.77" customHeight="true">
+    <row r="4" ht="97.23" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="U4" s="25"/>
     </row>
-    <row r="5" ht="117.77" customHeight="true">
+    <row r="5" ht="97.23" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="U5" s="25"/>
     </row>
-    <row r="6" ht="117.77" customHeight="true">
+    <row r="6" ht="97.23" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
       <c r="T6" s="21"/>
       <c r="U6" s="27"/>
     </row>
-    <row r="7" ht="117.77" customHeight="true">
+    <row r="7" ht="97.23" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="117.77" customHeight="true">
+    <row r="8" ht="97.23" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="U8" s="25"/>
     </row>
-    <row r="9" ht="117.77" customHeight="true">
+    <row r="9" ht="97.23" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="U9" s="25"/>
     </row>
-    <row r="10" ht="117.77" customHeight="true">
+    <row r="10" ht="97.23" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="27"/>
@@ -5908,7 +5908,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="27"/>
     </row>
-    <row r="11" ht="117.77" customHeight="true">
+    <row r="11" ht="97.23" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="117.77" customHeight="true">
+    <row r="12" ht="97.23" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="U12" s="25"/>
     </row>
-    <row r="13" ht="117.77" customHeight="true">
+    <row r="13" ht="97.23" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="117.77" customHeight="true">
+    <row r="14" ht="97.23" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
       <c r="T14" s="21"/>
       <c r="U14" s="27"/>
     </row>
-    <row r="15" ht="117.77" customHeight="true">
+    <row r="15" ht="97.23" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="117.77" customHeight="true">
+    <row r="16" ht="97.23" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="U16" s="25"/>
     </row>
-    <row r="17" ht="117.77" customHeight="true">
+    <row r="17" ht="97.23" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="U17" s="25"/>
     </row>
-    <row r="18" ht="117.77" customHeight="true">
+    <row r="18" ht="97.23" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -6416,6 +6416,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="38"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
 </worksheet>
 </file>